--- a/cds_files/BYU_CDS_2025-2026.xlsx
+++ b/cds_files/BYU_CDS_2025-2026.xlsx
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
     </row>
   </sheetData>
